--- a/Country_Classification.xlsx
+++ b/Country_Classification.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico\naroix\NaroIX-Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3827B5D-BE81-4570-8581-E693633A212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EB1850-7716-42D8-84CA-16D28EA75B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0C096B64-4C08-4A3D-8FEA-13FF5A622046}"/>
+    <workbookView xWindow="-13860" yWindow="-16308" windowWidth="29016" windowHeight="15696" xr2:uid="{0C096B64-4C08-4A3D-8FEA-13FF5A622046}"/>
   </bookViews>
   <sheets>
     <sheet name="Classification" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Classification!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Classification!$A$1:$C$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="53">
   <si>
     <t>Exchange Country Name</t>
   </si>
@@ -164,9 +164,6 @@
     <t>MEXICO</t>
   </si>
   <si>
-    <t>MOROCCO</t>
-  </si>
-  <si>
     <t>PHILIPPINES</t>
   </si>
   <si>
@@ -198,13 +195,16 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>PERU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -219,8 +219,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -251,14 +257,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -576,8 +581,8 @@
   <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,440 +593,451 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="B48" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C48" xr:uid="{D98FE50C-F6C7-47BE-A90E-267395B2A4FD}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C48">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>